--- a/public/templates/02_견적서_기성청구서_통합/견적서_기성청구서_통합.xlsx
+++ b/public/templates/02_견적서_기성청구서_통합/견적서_기성청구서_통합.xlsx
@@ -2483,108 +2483,148 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>○○아파트 지하주차장</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>주차장 환기휀</t>
+        </is>
+      </c>
       <c r="C3" s="15" t="str">
         <f aca="false">IF($B3="","",IFERROR(INDEX(품목마스터!$B$3:$B$102,MATCH($B3,품목마스터!$A$3:$A$102,0)),""))</f>
-        <v/>
+        <v>SF-500 / 1HP</v>
       </c>
       <c r="D3" s="15" t="str">
         <f aca="false">IF($B3="","",IFERROR(INDEX(품목마스터!$C$3:$C$102,MATCH($B3,품목마스터!$A$3:$A$102,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E3" s="13" t="str">
+        <v>대</v>
+      </c>
+      <c r="E3" s="13" t="n">
         <f aca="false">IF($B3="","",IFERROR(INDEX(품목마스터!$D$3:$D$102,MATCH($B3,품목마스터!$A$3:$A$102,0)),0))</f>
-        <v/>
-      </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="16" t="str">
+        <v>850000</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="16" t="n">
         <f aca="false">IF(OR($E3="",$F3=""),"",ROUND($E3*$F3,0))</f>
-        <v/>
-      </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="16" t="str">
+        <v>3400000</v>
+      </c>
+      <c r="H3" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="I3" s="16" t="n">
         <f aca="false">IF($G3="","",ROUND($G3*IF($H3="",0,$H3)/100,0))</f>
-        <v/>
-      </c>
-      <c r="J3" s="10"/>
-      <c r="K3" s="15" t="str">
+        <v>2040000</v>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>← 예시 행입니다. 지우고 쓰세요.</t>
+        </is>
+      </c>
+      <c r="K3" s="15" t="n">
         <f aca="false">IF($A3="","",COUNTIFS($A$3:$A3,$A3))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L3" s="15" t="str">
         <f aca="false">IF($A3="","",$A3&amp;"|"&amp;$K3)</f>
-        <v/>
+        <v>○○아파트 지하주차장|1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>○○아파트 지하주차장</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>급기 덕트</t>
+        </is>
+      </c>
       <c r="C4" s="15" t="str">
         <f aca="false">IF($B4="","",IFERROR(INDEX(품목마스터!$B$3:$B$102,MATCH($B4,품목마스터!$A$3:$A$102,0)),""))</f>
-        <v/>
+        <v>SPCC 0.6T</v>
       </c>
       <c r="D4" s="15" t="str">
         <f aca="false">IF($B4="","",IFERROR(INDEX(품목마스터!$C$3:$C$102,MATCH($B4,품목마스터!$A$3:$A$102,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E4" s="13" t="str">
+        <v>M</v>
+      </c>
+      <c r="E4" s="13" t="n">
         <f aca="false">IF($B4="","",IFERROR(INDEX(품목마스터!$D$3:$D$102,MATCH($B4,품목마스터!$A$3:$A$102,0)),0))</f>
-        <v/>
-      </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="16" t="str">
+        <v>42000</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G4" s="16" t="n">
         <f aca="false">IF(OR($E4="",$F4=""),"",ROUND($E4*$F4,0))</f>
-        <v/>
-      </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="16" t="str">
+        <v>5040000</v>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="I4" s="16" t="n">
         <f aca="false">IF($G4="","",ROUND($G4*IF($H4="",0,$H4)/100,0))</f>
-        <v/>
+        <v>3024000</v>
       </c>
       <c r="J4" s="10"/>
-      <c r="K4" s="15" t="str">
+      <c r="K4" s="15" t="n">
         <f aca="false">IF($A4="","",COUNTIFS($A$3:$A4,$A4))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="L4" s="15" t="str">
         <f aca="false">IF($A4="","",$A4&amp;"|"&amp;$K4)</f>
-        <v/>
+        <v>○○아파트 지하주차장|2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>○○아파트 지하주차장</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>배기 그릴</t>
+        </is>
+      </c>
       <c r="C5" s="15" t="str">
         <f aca="false">IF($B5="","",IFERROR(INDEX(품목마스터!$B$3:$B$102,MATCH($B5,품목마스터!$A$3:$A$102,0)),""))</f>
-        <v/>
+        <v>300x300</v>
       </c>
       <c r="D5" s="15" t="str">
         <f aca="false">IF($B5="","",IFERROR(INDEX(품목마스터!$C$3:$C$102,MATCH($B5,품목마스터!$A$3:$A$102,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E5" s="13" t="str">
+        <v>EA</v>
+      </c>
+      <c r="E5" s="13" t="n">
         <f aca="false">IF($B5="","",IFERROR(INDEX(품목마스터!$D$3:$D$102,MATCH($B5,품목마스터!$A$3:$A$102,0)),0))</f>
-        <v/>
-      </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="16" t="str">
+        <v>18000</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="G5" s="16" t="n">
         <f aca="false">IF(OR($E5="",$F5=""),"",ROUND($E5*$F5,0))</f>
-        <v/>
-      </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="16" t="str">
+        <v>432000</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="I5" s="16" t="n">
         <f aca="false">IF($G5="","",ROUND($G5*IF($H5="",0,$H5)/100,0))</f>
-        <v/>
+        <v>216000</v>
       </c>
       <c r="J5" s="10"/>
-      <c r="K5" s="15" t="str">
+      <c r="K5" s="15" t="n">
         <f aca="false">IF($A5="","",COUNTIFS($A$3:$A5,$A5))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="L5" s="15" t="str">
         <f aca="false">IF($A5="","",$A5&amp;"|"&amp;$K5)</f>
-        <v/>
+        <v>○○아파트 지하주차장|3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13048,7 +13088,7 @@
       </c>
       <c r="F3" s="21" t="n">
         <f aca="true">TODAY()</f>
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="G3" s="21"/>
     </row>
@@ -13149,27 +13189,27 @@
       </c>
       <c r="B11" s="15" t="str">
         <f aca="false">IFERROR(INDEX(내역입력!$B$3:$B$302,MATCH($C$3&amp;"|"&amp;1,내역입력!$L$3:$L$302,0)),"")</f>
-        <v/>
+        <v>주차장 환기휀</v>
       </c>
       <c r="C11" s="15" t="str">
         <f aca="false">IF($B11="","",IFERROR(INDEX(내역입력!$C$3:$C$302,MATCH($C$3&amp;"|"&amp;1,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
+        <v>SF-500 / 1HP</v>
       </c>
       <c r="D11" s="27" t="str">
         <f aca="false">IF($B11="","",IFERROR(INDEX(내역입력!$D$3:$D$302,MATCH($C$3&amp;"|"&amp;1,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E11" s="28" t="str">
+        <v>대</v>
+      </c>
+      <c r="E11" s="28" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(내역입력!$F$3:$F$302,MATCH($C$3&amp;"|"&amp;1,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F11" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="F11" s="16" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(내역입력!$E$3:$E$302,MATCH($C$3&amp;"|"&amp;1,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G11" s="16" t="str">
+        <v>850000</v>
+      </c>
+      <c r="G11" s="16" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(내역입력!$G$3:$G$302,MATCH($C$3&amp;"|"&amp;1,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
+        <v>3400000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13178,27 +13218,27 @@
       </c>
       <c r="B12" s="15" t="str">
         <f aca="false">IFERROR(INDEX(내역입력!$B$3:$B$302,MATCH($C$3&amp;"|"&amp;2,내역입력!$L$3:$L$302,0)),"")</f>
-        <v/>
+        <v>급기 덕트</v>
       </c>
       <c r="C12" s="15" t="str">
         <f aca="false">IF($B12="","",IFERROR(INDEX(내역입력!$C$3:$C$302,MATCH($C$3&amp;"|"&amp;2,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
+        <v>SPCC 0.6T</v>
       </c>
       <c r="D12" s="27" t="str">
         <f aca="false">IF($B12="","",IFERROR(INDEX(내역입력!$D$3:$D$302,MATCH($C$3&amp;"|"&amp;2,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E12" s="28" t="str">
+        <v>M</v>
+      </c>
+      <c r="E12" s="28" t="n">
         <f aca="false">IF($B12="","",IFERROR(INDEX(내역입력!$F$3:$F$302,MATCH($C$3&amp;"|"&amp;2,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F12" s="16" t="str">
+        <v>120</v>
+      </c>
+      <c r="F12" s="16" t="n">
         <f aca="false">IF($B12="","",IFERROR(INDEX(내역입력!$E$3:$E$302,MATCH($C$3&amp;"|"&amp;2,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G12" s="16" t="str">
+        <v>42000</v>
+      </c>
+      <c r="G12" s="16" t="n">
         <f aca="false">IF($B12="","",IFERROR(INDEX(내역입력!$G$3:$G$302,MATCH($C$3&amp;"|"&amp;2,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
+        <v>5040000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13207,27 +13247,27 @@
       </c>
       <c r="B13" s="15" t="str">
         <f aca="false">IFERROR(INDEX(내역입력!$B$3:$B$302,MATCH($C$3&amp;"|"&amp;3,내역입력!$L$3:$L$302,0)),"")</f>
-        <v/>
+        <v>배기 그릴</v>
       </c>
       <c r="C13" s="15" t="str">
         <f aca="false">IF($B13="","",IFERROR(INDEX(내역입력!$C$3:$C$302,MATCH($C$3&amp;"|"&amp;3,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
+        <v>300x300</v>
       </c>
       <c r="D13" s="27" t="str">
         <f aca="false">IF($B13="","",IFERROR(INDEX(내역입력!$D$3:$D$302,MATCH($C$3&amp;"|"&amp;3,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E13" s="28" t="str">
+        <v>EA</v>
+      </c>
+      <c r="E13" s="28" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(내역입력!$F$3:$F$302,MATCH($C$3&amp;"|"&amp;3,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F13" s="16" t="str">
+        <v>24</v>
+      </c>
+      <c r="F13" s="16" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(내역입력!$E$3:$E$302,MATCH($C$3&amp;"|"&amp;3,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G13" s="16" t="str">
+        <v>18000</v>
+      </c>
+      <c r="G13" s="16" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(내역입력!$G$3:$G$302,MATCH($C$3&amp;"|"&amp;3,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
+        <v>432000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13733,7 +13773,7 @@
       <c r="F31" s="23"/>
       <c r="G31" s="29" t="n">
         <f aca="false">SUM(G11:G30)</f>
-        <v>0</v>
+        <v>8872000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13746,7 +13786,7 @@
       <c r="F32" s="23"/>
       <c r="G32" s="29" t="n">
         <f aca="false">ROUND(G31*기초정보!$C$13,0)</f>
-        <v>0</v>
+        <v>887200</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13759,7 +13799,7 @@
       <c r="F33" s="30"/>
       <c r="G33" s="31" t="n">
         <f aca="false">G31+G32</f>
-        <v>0</v>
+        <v>9759200</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13845,7 +13885,7 @@
       </c>
       <c r="F3" s="21" t="n">
         <f aca="true">TODAY()</f>
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="G3" s="21"/>
     </row>
@@ -13946,27 +13986,27 @@
       </c>
       <c r="B11" s="15" t="str">
         <f aca="false">IFERROR(INDEX(내역입력!$B$3:$B$302,MATCH($C$3&amp;"|"&amp;1,내역입력!$L$3:$L$302,0)),"")</f>
-        <v/>
+        <v>주차장 환기휀</v>
       </c>
       <c r="C11" s="15" t="str">
         <f aca="false">IF($B11="","",IFERROR(INDEX(내역입력!$C$3:$C$302,MATCH($C$3&amp;"|"&amp;1,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
+        <v>SF-500 / 1HP</v>
       </c>
       <c r="D11" s="27" t="str">
         <f aca="false">IF($B11="","",IFERROR(INDEX(내역입력!$D$3:$D$302,MATCH($C$3&amp;"|"&amp;1,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E11" s="28" t="str">
+        <v>대</v>
+      </c>
+      <c r="E11" s="28" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(내역입력!$F$3:$F$302,MATCH($C$3&amp;"|"&amp;1,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F11" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="F11" s="16" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(내역입력!$E$3:$E$302,MATCH($C$3&amp;"|"&amp;1,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G11" s="16" t="str">
+        <v>850000</v>
+      </c>
+      <c r="G11" s="16" t="n">
         <f aca="false">IF($B11="","",IFERROR(INDEX(내역입력!$I$3:$I$302,MATCH($C$3&amp;"|"&amp;1,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
+        <v>2040000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13975,27 +14015,27 @@
       </c>
       <c r="B12" s="15" t="str">
         <f aca="false">IFERROR(INDEX(내역입력!$B$3:$B$302,MATCH($C$3&amp;"|"&amp;2,내역입력!$L$3:$L$302,0)),"")</f>
-        <v/>
+        <v>급기 덕트</v>
       </c>
       <c r="C12" s="15" t="str">
         <f aca="false">IF($B12="","",IFERROR(INDEX(내역입력!$C$3:$C$302,MATCH($C$3&amp;"|"&amp;2,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
+        <v>SPCC 0.6T</v>
       </c>
       <c r="D12" s="27" t="str">
         <f aca="false">IF($B12="","",IFERROR(INDEX(내역입력!$D$3:$D$302,MATCH($C$3&amp;"|"&amp;2,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E12" s="28" t="str">
+        <v>M</v>
+      </c>
+      <c r="E12" s="28" t="n">
         <f aca="false">IF($B12="","",IFERROR(INDEX(내역입력!$F$3:$F$302,MATCH($C$3&amp;"|"&amp;2,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F12" s="16" t="str">
+        <v>120</v>
+      </c>
+      <c r="F12" s="16" t="n">
         <f aca="false">IF($B12="","",IFERROR(INDEX(내역입력!$E$3:$E$302,MATCH($C$3&amp;"|"&amp;2,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G12" s="16" t="str">
+        <v>42000</v>
+      </c>
+      <c r="G12" s="16" t="n">
         <f aca="false">IF($B12="","",IFERROR(INDEX(내역입력!$I$3:$I$302,MATCH($C$3&amp;"|"&amp;2,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
+        <v>3024000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14004,27 +14044,27 @@
       </c>
       <c r="B13" s="15" t="str">
         <f aca="false">IFERROR(INDEX(내역입력!$B$3:$B$302,MATCH($C$3&amp;"|"&amp;3,내역입력!$L$3:$L$302,0)),"")</f>
-        <v/>
+        <v>배기 그릴</v>
       </c>
       <c r="C13" s="15" t="str">
         <f aca="false">IF($B13="","",IFERROR(INDEX(내역입력!$C$3:$C$302,MATCH($C$3&amp;"|"&amp;3,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
+        <v>300x300</v>
       </c>
       <c r="D13" s="27" t="str">
         <f aca="false">IF($B13="","",IFERROR(INDEX(내역입력!$D$3:$D$302,MATCH($C$3&amp;"|"&amp;3,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E13" s="28" t="str">
+        <v>EA</v>
+      </c>
+      <c r="E13" s="28" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(내역입력!$F$3:$F$302,MATCH($C$3&amp;"|"&amp;3,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="F13" s="16" t="str">
+        <v>24</v>
+      </c>
+      <c r="F13" s="16" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(내역입력!$E$3:$E$302,MATCH($C$3&amp;"|"&amp;3,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G13" s="16" t="str">
+        <v>18000</v>
+      </c>
+      <c r="G13" s="16" t="n">
         <f aca="false">IF($B13="","",IFERROR(INDEX(내역입력!$I$3:$I$302,MATCH($C$3&amp;"|"&amp;3,내역입력!$L$3:$L$302,0)),""))</f>
-        <v/>
+        <v>216000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14530,7 +14570,7 @@
       <c r="F31" s="23"/>
       <c r="G31" s="29" t="n">
         <f aca="false">SUM(G11:G30)</f>
-        <v>0</v>
+        <v>5280000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14543,7 +14583,7 @@
       <c r="F32" s="23"/>
       <c r="G32" s="29" t="n">
         <f aca="false">ROUND(G31*기초정보!$C$13,0)</f>
-        <v>0</v>
+        <v>528000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14556,7 +14596,7 @@
       <c r="F33" s="30"/>
       <c r="G33" s="31" t="n">
         <f aca="false">G31+G32</f>
-        <v>0</v>
+        <v>5808000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
